--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00734B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00734B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{275D463A-2F4F-4A21-B2EC-05D65ADDA021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7692C2C7-39D7-4D17-91A4-F70BC768A94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{131783ED-14B8-4FFE-8844-6C8972C90CC1}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{13B2C73A-3355-40D0-9293-C1B33C78E4E3}"/>
   </bookViews>
   <sheets>
     <sheet name="00734B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1609,20 +1609,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1B85B07-1CC2-4DDB-B177-B301A2E549FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B73B823-4F2A-4EC3-AD8B-EC8A9F674F5E}">
   <dimension ref="A1:R45"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1650,7 +1650,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1680,7 +1680,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1776,7 +1776,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1856,7 +1856,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>4.5199999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2021</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>27</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>27</v>
       </c>
@@ -3246,7 +3246,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>27</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2020</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>3.65</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>27</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>27</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>27</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>27</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>2019</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>27</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>27</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>27</v>
       </c>
@@ -3802,7 +3802,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>27</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="51">
         <v>2018</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>27</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="49" t="s">
         <v>74</v>
       </c>
